--- a/Main/AUT_EEC_results/AUT_EEC_SIDIS_a1.00_b1.00_x0.01_Q100_LO.xlsx
+++ b/Main/AUT_EEC_results/AUT_EEC_SIDIS_a1.00_b1.00_x0.01_Q100_LO.xlsx
@@ -455,10 +455,10 @@
         <v>1</v>
       </c>
       <c r="B2" t="n">
-        <v>0.0006530455033736065</v>
+        <v>0.0003032497614114147</v>
       </c>
       <c r="C2" t="n">
-        <v>0.0006530455033736065</v>
+        <v>0.0003032497614114147</v>
       </c>
       <c r="D2" t="n">
         <v>0</v>
@@ -469,10 +469,10 @@
         <v>2</v>
       </c>
       <c r="B3" t="n">
-        <v>0.001395383745699498</v>
+        <v>0.0006617140179310354</v>
       </c>
       <c r="C3" t="n">
-        <v>0.001395383745699498</v>
+        <v>0.0006617140179310354</v>
       </c>
       <c r="D3" t="n">
         <v>0</v>
@@ -483,10 +483,10 @@
         <v>3</v>
       </c>
       <c r="B4" t="n">
-        <v>0.002671955561027822</v>
+        <v>0.001260079357869231</v>
       </c>
       <c r="C4" t="n">
-        <v>0.002671955561027822</v>
+        <v>0.001260079357869231</v>
       </c>
       <c r="D4" t="n">
         <v>0</v>
@@ -497,10 +497,10 @@
         <v>4</v>
       </c>
       <c r="B5" t="n">
-        <v>0.003860833613784043</v>
+        <v>0.001825508248217908</v>
       </c>
       <c r="C5" t="n">
-        <v>0.003860833613784043</v>
+        <v>0.001825508248217908</v>
       </c>
       <c r="D5" t="n">
         <v>0</v>
@@ -511,10 +511,10 @@
         <v>5</v>
       </c>
       <c r="B6" t="n">
-        <v>0.004126209095988749</v>
+        <v>0.001949587492802779</v>
       </c>
       <c r="C6" t="n">
-        <v>0.004126209095988749</v>
+        <v>0.001949587492802779</v>
       </c>
       <c r="D6" t="n">
         <v>0</v>
@@ -525,10 +525,10 @@
         <v>6</v>
       </c>
       <c r="B7" t="n">
-        <v>0.00382097011468747</v>
+        <v>0.001805090813741054</v>
       </c>
       <c r="C7" t="n">
-        <v>0.00382097011468747</v>
+        <v>0.001805090813741054</v>
       </c>
       <c r="D7" t="n">
         <v>0</v>
@@ -539,10 +539,10 @@
         <v>7</v>
       </c>
       <c r="B8" t="n">
-        <v>0.003521018261879377</v>
+        <v>0.001663759815955862</v>
       </c>
       <c r="C8" t="n">
-        <v>0.003521018261879377</v>
+        <v>0.001663759815955862</v>
       </c>
       <c r="D8" t="n">
         <v>0</v>
@@ -553,10 +553,10 @@
         <v>8</v>
       </c>
       <c r="B9" t="n">
-        <v>0.003305838482527493</v>
+        <v>0.00156490404095759</v>
       </c>
       <c r="C9" t="n">
-        <v>0.003305838482527493</v>
+        <v>0.00156490404095759</v>
       </c>
       <c r="D9" t="n">
         <v>0</v>
